--- a/3.2/水果与健康/数据绘图.xlsx
+++ b/3.2/水果与健康/数据绘图.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DeskTop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NJAU_CS\3.2\水果与健康\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3538A06D-A77A-4B2A-915C-C3CB6B51D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598305D0-D934-4D77-8D75-D6FF7B364E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6672" yWindow="3036" windowWidth="19440" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4584" yWindow="1380" windowWidth="19440" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>年份</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,14 @@
   </si>
   <si>
     <t>[1]徐维盛,李东,刘静,杨月欣.ORAC法对12种水果总抗氧化能力评价研究[J].食品工业,2014,35(1):247-250</t>
+  </si>
+  <si>
+    <t>花青素提取物浓度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对α-葡萄糖苷酶抑制率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -645,7 +653,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1745,6 +1753,323 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>对α-葡萄糖苷酶抑制率</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$34:$A$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$34:$B$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>92.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9AED-4D79-A7C6-162BF7FE0315}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="85509376"/>
+        <c:axId val="85509856"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="85509376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85509856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="85509856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85509376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1825,6 +2150,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -2812,6 +3177,522 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2900,6 +3781,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05B4EEF6-DA01-740F-34BE-8BC623C95B2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3171,7 +4088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3329,6 +4246,46 @@
       </c>
       <c r="B29">
         <v>1010.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>100</v>
+      </c>
+      <c r="B36">
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>200</v>
+      </c>
+      <c r="B37">
+        <v>92.1</v>
       </c>
     </row>
   </sheetData>
